--- a/config/excel/CfgCombatAnimationCues.xlsx
+++ b/config/excel/CfgCombatAnimationCues.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatAnimationCues" sheetId="1" r:id="R7c60fe56fa054de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatAnimationCues" sheetId="1" r:id="R756aa3aa10b247c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +36,13 @@
       <x:color rgb="FF0000FF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +57,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -63,7 +101,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -118,6 +156,36 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -346,86 +414,142 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>IsAttack</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>StateName</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>StatePath</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="22" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="22" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="str">
+      <x:c r="C2" s="22" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="10" t="str">
+      <x:c r="D2" s="22" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="23" t="str">
         <x:v># 战斗Cue事件编号。</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="23" t="str">
         <x:v>是否采样攻击动作。</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="23" t="str">
         <x:v>动作显示名称。</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="23" t="str">
         <x:v>Animator完整状态路径。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="6" t="n">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
-        <x:v>Attack</x:v>
-      </x:c>
-      <x:c r="D4" s="13" t="str">
-        <x:v>Base Layer.Attack</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="6" t="n">
+      <x:c r="C4" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="19" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="str">
-        <x:v>Attack</x:v>
-      </x:c>
-      <x:c r="D5" s="13" t="str">
-        <x:v>Base Layer.Attack</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="6" t="n">
+      <x:c r="C5" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="19" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="13" t="str">
-        <x:v>Attack</x:v>
-      </x:c>
-      <x:c r="D6" s="13" t="str">
+      <x:c r="C6" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="19" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
         <x:v>Base Layer.Attack</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgCombatAnimationCues.xlsx
+++ b/config/excel/CfgCombatAnimationCues.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatAnimationCues" sheetId="1" r:id="R756aa3aa10b247c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatAnimationCues" sheetId="1" r:id="Rd537a6e073e94dbb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,6 +41,11 @@
       <x:color rgb="FF215E99"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="11">
     <x:fill>
@@ -101,7 +106,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -188,6 +193,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -553,6 +559,34 @@
         <x:v>Base Layer.Attack</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D11" s="24" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="str">
+        <x:v>Base Layer.Attack</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
